--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -8,15 +8,70 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>Finances</t>
+  </si>
+  <si>
+    <t>filler variable</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sept</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>Total Yearly</t>
+  </si>
+  <si>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -24,13 +79,48 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3FF79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46C732"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -45,8 +135,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -341,18 +434,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="15" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -14,12 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Finances</t>
-  </si>
-  <si>
-    <t>filler variable</t>
   </si>
   <si>
     <t>Jan</t>
@@ -71,6 +68,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -135,9 +135,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -446,72 +447,75 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="B1" s="2">
+        <v>43101</v>
+      </c>
+      <c r="C1" s="2">
+        <v>43103</v>
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Finances</t>
   </si>
@@ -62,6 +62,21 @@
   </si>
   <si>
     <t>Income</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>Toiletries</t>
+  </si>
+  <si>
+    <t>Income Total</t>
+  </si>
+  <si>
+    <t>Expenses</t>
+  </si>
+  <si>
+    <t>Total Expenses</t>
   </si>
 </sst>
 </file>
@@ -71,7 +86,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,8 +117,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -122,6 +145,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1551BA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5352E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -135,12 +170,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,10 +474,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
     <col min="2" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="15" width="15.7109375" customWidth="1"/>
   </cols>
@@ -517,6 +556,45 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Finances</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Expenses</t>
+  </si>
+  <si>
+    <t>Clothes</t>
   </si>
   <si>
     <t>Total Expenses</t>
@@ -474,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -591,8 +594,13 @@
       <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="5" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="8" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Finances</t>
   </si>
@@ -80,14 +80,21 @@
   </si>
   <si>
     <t>Total Expenses</t>
+  </si>
+  <si>
+    <t>Savings</t>
+  </si>
+  <si>
+    <t>Percent Savings</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -129,7 +136,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -157,6 +164,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5352E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5AC2E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF15BA30"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -173,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -183,6 +202,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -603,6 +624,16 @@
         <v>21</v>
       </c>
     </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>Finances</t>
   </si>
@@ -64,10 +64,10 @@
     <t>Income</t>
   </si>
   <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>Toiletries</t>
+    <t>FOOD</t>
+  </si>
+  <si>
+    <t>TOILETRIES</t>
   </si>
   <si>
     <t>Income Total</t>
@@ -76,7 +76,7 @@
     <t>Expenses</t>
   </si>
   <si>
-    <t>Clothes</t>
+    <t>CLOTHES</t>
   </si>
   <si>
     <t>Total Expenses</t>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -591,46 +591,51 @@
       </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="7" t="s">
+    <row r="8" spans="1:15">
+      <c r="A8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="8" t="s">
+    <row r="10" spans="1:15">
+      <c r="A10" s="8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="9" t="s">
+    <row r="11" spans="1:15">
+      <c r="A11" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="10" t="s">
+    <row r="12" spans="1:15">
+      <c r="A12" s="10" t="s">
         <v>23</v>
       </c>
     </row>

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Finances</t>
   </si>
@@ -92,9 +92,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.00%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -192,18 +193,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -584,58 +586,62 @@
       <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="B4" s="6">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="B5" s="6">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="5" t="s">
-        <v>17</v>
+      <c r="A6" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="A7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
+      <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="6">
+        <v>78.98</v>
+      </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="5" t="s">
-        <v>20</v>
+      <c r="A9" s="9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="8" t="s">
-        <v>21</v>
+      <c r="A10" s="10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
     </row>

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -602,6 +602,62 @@
       <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
+      <c r="B6" s="6">
+        <f>SUM(B4, B5)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="6">
+        <f>SUM(C4, C5)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <f>SUM(D4, D5)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <f>SUM(E4, E5)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <f>SUM(F4, F5)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <f>SUM(G4, G5)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <f>SUM(H4, H5)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <f>SUM(I4, I5)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <f>SUM(J4, J5)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="6">
+        <f>SUM(K4, K5)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="6">
+        <f>SUM(L4, L5)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
+        <f>SUM(M4, M5)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="6">
+        <f>SUM(N4, N5)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <f>SUM(O4, O5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="8" t="s">

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -603,59 +603,59 @@
         <v>18</v>
       </c>
       <c r="B6" s="6">
-        <f>SUM(B4, B5)</f>
+        <f>SUM(B3, B5)</f>
         <v>0</v>
       </c>
       <c r="C6" s="6">
-        <f>SUM(C4, C5)</f>
+        <f>SUM(C3, C5)</f>
         <v>0</v>
       </c>
       <c r="D6" s="6">
-        <f>SUM(D4, D5)</f>
+        <f>SUM(D3, D5)</f>
         <v>0</v>
       </c>
       <c r="E6" s="6">
-        <f>SUM(E4, E5)</f>
+        <f>SUM(E3, E5)</f>
         <v>0</v>
       </c>
       <c r="F6" s="6">
-        <f>SUM(F4, F5)</f>
+        <f>SUM(F3, F5)</f>
         <v>0</v>
       </c>
       <c r="G6" s="6">
-        <f>SUM(G4, G5)</f>
+        <f>SUM(G3, G5)</f>
         <v>0</v>
       </c>
       <c r="H6" s="6">
-        <f>SUM(H4, H5)</f>
+        <f>SUM(H3, H5)</f>
         <v>0</v>
       </c>
       <c r="I6" s="6">
-        <f>SUM(I4, I5)</f>
+        <f>SUM(I3, I5)</f>
         <v>0</v>
       </c>
       <c r="J6" s="6">
-        <f>SUM(J4, J5)</f>
+        <f>SUM(J3, J5)</f>
         <v>0</v>
       </c>
       <c r="K6" s="6">
-        <f>SUM(K4, K5)</f>
+        <f>SUM(K3, K5)</f>
         <v>0</v>
       </c>
       <c r="L6" s="6">
-        <f>SUM(L4, L5)</f>
+        <f>SUM(L3, L5)</f>
         <v>0</v>
       </c>
       <c r="M6" s="6">
-        <f>SUM(M4, M5)</f>
+        <f>SUM(M3, M5)</f>
         <v>0</v>
       </c>
       <c r="N6" s="6">
-        <f>SUM(N4, N5)</f>
+        <f>SUM(N3, N5)</f>
         <v>0</v>
       </c>
       <c r="O6" s="6">
-        <f>SUM(O4, O5)</f>
+        <f>SUM(O3, O5)</f>
         <v>0</v>
       </c>
     </row>
@@ -690,6 +690,62 @@
       <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
+      <c r="B9" s="6">
+        <f>SUM(B7, B8)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="6">
+        <f>SUM(C7, C8)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <f>SUM(D7, D8)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <f>SUM(E7, E8)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <f>SUM(F7, F8)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <f>SUM(G7, G8)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <f>SUM(H7, H8)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
+        <f>SUM(I7, I8)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <f>SUM(J7, J8)</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="6">
+        <f>SUM(K7, K8)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="6">
+        <f>SUM(L7, L8)</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
+        <f>SUM(M7, M8)</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="6">
+        <f>SUM(N7, N8)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <f>SUM(O7, O8)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="10" t="s">

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -751,6 +751,62 @@
       <c r="A10" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="B10" s="6">
+        <f>B6-B9</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="6">
+        <f>C6-C9</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <f>D6-D9</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <f>E6-E9</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <f>F6-F9</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
+        <f>G6-G9</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
+        <f>H6-H9</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
+        <f>I6-I9</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <f>J6-J9</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <f>K6-K9</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="6">
+        <f>L6-L9</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="6">
+        <f>M6-M9</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="6">
+        <f>N6-N9</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <f>O6-O9</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="11" t="s">

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -812,6 +812,62 @@
       <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
+      <c r="B11" s="11">
+        <f>B6/B10</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="11">
+        <f>C6/C10</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <f>D6/D10</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="11">
+        <f>E6/E10</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <f>F6/F10</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11">
+        <f>G6/G10</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <f>H6/H10</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="11">
+        <f>I6/I10</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="11">
+        <f>J6/J10</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="11">
+        <f>K6/K10</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="11">
+        <f>L6/L10</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="11">
+        <f>M6/M10</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="11">
+        <f>N6/N10</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="11">
+        <f>O6/O10</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -602,59 +602,59 @@
       <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <f>SUM(B3, B5)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <f>SUM(C3, C5)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="7">
         <f>SUM(D3, D5)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <f>SUM(E3, E5)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <f>SUM(F3, F5)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <f>SUM(G3, G5)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="7">
         <f>SUM(H3, H5)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <f>SUM(I3, I5)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="7">
         <f>SUM(J3, J5)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="7">
         <f>SUM(K3, K5)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="7">
         <f>SUM(L3, L5)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="7">
         <f>SUM(M3, M5)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="7">
         <f>SUM(N3, N5)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="7">
         <f>SUM(O3, O5)</f>
         <v>0</v>
       </c>
@@ -690,59 +690,59 @@
       <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="9">
         <f>SUM(B7, B8)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="9">
         <f>SUM(C7, C8)</f>
         <v>0</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="9">
         <f>SUM(D7, D8)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="9">
         <f>SUM(E7, E8)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="9">
         <f>SUM(F7, F8)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="9">
         <f>SUM(G7, G8)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="9">
         <f>SUM(H7, H8)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="9">
         <f>SUM(I7, I8)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="9">
         <f>SUM(J7, J8)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="9">
         <f>SUM(K7, K8)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="9">
         <f>SUM(L7, L8)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="9">
         <f>SUM(M7, M8)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="6">
+      <c r="N9" s="9">
         <f>SUM(N7, N8)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="9">
         <f>SUM(O7, O8)</f>
         <v>0</v>
       </c>
@@ -751,59 +751,59 @@
       <c r="A10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="10">
         <f>B6-B9</f>
         <v>0</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="10">
         <f>C6-C9</f>
         <v>0</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="10">
         <f>D6-D9</f>
         <v>0</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="10">
         <f>E6-E9</f>
         <v>0</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="10">
         <f>F6-F9</f>
         <v>0</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="10">
         <f>G6-G9</f>
         <v>0</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="10">
         <f>H6-H9</f>
         <v>0</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="10">
         <f>I6-I9</f>
         <v>0</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="10">
         <f>J6-J9</f>
         <v>0</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="10">
         <f>K6-K9</f>
         <v>0</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="10">
         <f>L6-L9</f>
         <v>0</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="10">
         <f>M6-M9</f>
         <v>0</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="10">
         <f>N6-N9</f>
         <v>0</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="10">
         <f>O6-O9</f>
         <v>0</v>
       </c>

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -199,10 +199,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -567,123 +567,106 @@
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>5.5</v>
       </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="6">
-        <v>22</v>
-      </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="7">
-        <f>SUM(B3, B5)</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="7">
-        <f>SUM(C3, C5)</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="7">
-        <f>SUM(D3, D5)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="7">
-        <f>SUM(E3, E5)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
-        <f>SUM(F3, F5)</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <f>SUM(G3, G5)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
-        <f>SUM(H3, H5)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="7">
-        <f>SUM(I3, I5)</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="7">
-        <f>SUM(J3, J5)</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <f>SUM(K3, K5)</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <f>SUM(L3, L5)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <f>SUM(M3, M5)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <f>SUM(N3, N5)</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="7">
-        <f>SUM(O3, O5)</f>
+      <c r="B6" s="8">
+        <f>SUM(B3:B5)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="8">
+        <f>SUM(C3:C5)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="8">
+        <f>SUM(D3:D5)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <f>SUM(E3:E5)</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
+        <f>SUM(F3:F5)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <f>SUM(G3:G5)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <f>SUM(H3:H5)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="8">
+        <f>SUM(I3:I5)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <f>SUM(J3:J5)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
+        <f>SUM(K3:K5)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="8">
+        <f>SUM(L3:L5)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="8">
+        <f>SUM(M3:M5)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="8">
+        <f>SUM(N3:N5)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="8">
+        <f>SUM(O3:O5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
+      <c r="B7" s="7">
+        <v>78.98</v>
+      </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="6">
-        <v>78.98</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -691,59 +674,59 @@
         <v>21</v>
       </c>
       <c r="B9" s="9">
-        <f>SUM(B7, B8)</f>
+        <f>SUM(B7:B8)</f>
         <v>0</v>
       </c>
       <c r="C9" s="9">
-        <f>SUM(C7, C8)</f>
+        <f>SUM(C7:C8)</f>
         <v>0</v>
       </c>
       <c r="D9" s="9">
-        <f>SUM(D7, D8)</f>
+        <f>SUM(D7:D8)</f>
         <v>0</v>
       </c>
       <c r="E9" s="9">
-        <f>SUM(E7, E8)</f>
+        <f>SUM(E7:E8)</f>
         <v>0</v>
       </c>
       <c r="F9" s="9">
-        <f>SUM(F7, F8)</f>
+        <f>SUM(F7:F8)</f>
         <v>0</v>
       </c>
       <c r="G9" s="9">
-        <f>SUM(G7, G8)</f>
+        <f>SUM(G7:G8)</f>
         <v>0</v>
       </c>
       <c r="H9" s="9">
-        <f>SUM(H7, H8)</f>
+        <f>SUM(H7:H8)</f>
         <v>0</v>
       </c>
       <c r="I9" s="9">
-        <f>SUM(I7, I8)</f>
+        <f>SUM(I7:I8)</f>
         <v>0</v>
       </c>
       <c r="J9" s="9">
-        <f>SUM(J7, J8)</f>
+        <f>SUM(J7:J8)</f>
         <v>0</v>
       </c>
       <c r="K9" s="9">
-        <f>SUM(K7, K8)</f>
+        <f>SUM(K7:K8)</f>
         <v>0</v>
       </c>
       <c r="L9" s="9">
-        <f>SUM(L7, L8)</f>
+        <f>SUM(L7:L8)</f>
         <v>0</v>
       </c>
       <c r="M9" s="9">
-        <f>SUM(M7, M8)</f>
+        <f>SUM(M7:M8)</f>
         <v>0</v>
       </c>
       <c r="N9" s="9">
-        <f>SUM(N7, N8)</f>
+        <f>SUM(N7:N8)</f>
         <v>0</v>
       </c>
       <c r="O9" s="9">
-        <f>SUM(O7, O8)</f>
+        <f>SUM(O7:O8)</f>
         <v>0</v>
       </c>
     </row>

--- a/test_worksheet.xlsx
+++ b/test_worksheet.xlsx
@@ -199,10 +199,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -567,105 +567,118 @@
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>5.5</v>
       </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <f>SUM(B3:B5)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <f>SUM(C3:C5)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <f>SUM(D3:D5)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f>SUM(E3:E5)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <f>SUM(F3:F5)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <f>SUM(G3:G5)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <f>SUM(H3:H5)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <f>SUM(I3:I5)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <f>SUM(J3:J5)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <f>SUM(K3:K5)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="7">
         <f>SUM(L3:L5)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="7">
         <f>SUM(M3:M5)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="7">
         <f>SUM(N3:N5)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <f>SUM(O3:O5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>78.98</v>
       </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
     </row>
